--- a/CLNDC.xlsx
+++ b/CLNDC.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>NOM COMERCIAL</t>
   </si>
@@ -280,6 +280,21 @@
   </si>
   <si>
     <t>ZEMZEM</t>
+  </si>
+  <si>
+    <t>BOULOUIZ TOURISME ET VOYAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">411ND011  </t>
+  </si>
+  <si>
+    <t>BENFRIHA TOURS</t>
+  </si>
+  <si>
+    <t>LEJDAR TRAVEL AGENCY</t>
+  </si>
+  <si>
+    <t>LEJDAR TRAVEL</t>
   </si>
 </sst>
 </file>
@@ -315,7 +330,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -351,12 +366,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -372,12 +400,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -395,62 +424,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -751,10 +724,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -774,143 +747,143 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>73</v>
+      <c r="A2" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1">
         <v>411</v>
       </c>
-      <c r="D2" s="2">
-        <v>41100011</v>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>74</v>
+      <c r="A3" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1">
         <v>411</v>
       </c>
       <c r="D3" s="2">
-        <v>41100620</v>
+        <v>41100290</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>84</v>
+      <c r="A4" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
         <v>411</v>
       </c>
-      <c r="D4" s="1">
-        <v>41100009</v>
+      <c r="D4" s="2">
+        <v>41100265</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>85</v>
+      <c r="A5" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1">
         <v>411</v>
       </c>
-      <c r="D5" s="1">
-        <v>41100661</v>
+      <c r="D5" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1">
         <v>411</v>
       </c>
       <c r="D6" s="2">
-        <v>41100118</v>
+        <v>41100185</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C7" s="1">
         <v>411</v>
       </c>
-      <c r="D7" s="2">
-        <v>41100371</v>
+      <c r="D7" s="4">
+        <v>41100313</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1">
         <v>411</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
+      <c r="D8" s="2">
+        <v>41100010</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1">
         <v>411</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
+      <c r="D9" s="2">
+        <v>41100003</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
+      <c r="A10" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="C10" s="1">
         <v>411</v>
       </c>
       <c r="D10" s="2">
-        <v>41100125</v>
+        <v>41100620</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1">
         <v>411</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>14</v>
+      <c r="D11" s="2">
+        <v>41100305</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
@@ -921,16 +894,16 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1">
         <v>411</v>
       </c>
-      <c r="D12" s="2">
-        <v>41100096</v>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="K12">
         <v>181142</v>
@@ -941,16 +914,16 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1">
         <v>411</v>
       </c>
-      <c r="D13" s="2">
-        <v>41100328</v>
+      <c r="D13" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="K13">
         <v>181143</v>
@@ -961,16 +934,16 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1">
         <v>411</v>
       </c>
-      <c r="D14" s="2">
-        <v>41100319</v>
+      <c r="D14" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="K14">
         <v>181144</v>
@@ -981,16 +954,16 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1">
         <v>411</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>21</v>
+      <c r="D15" s="4">
+        <v>41100203</v>
       </c>
       <c r="K15">
         <v>181145</v>
@@ -1001,16 +974,16 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>411</v>
       </c>
-      <c r="D16" s="2">
-        <v>41100282</v>
+      <c r="D16" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="K16">
         <v>181146</v>
@@ -1021,16 +994,16 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
         <v>411</v>
       </c>
       <c r="D17" s="2">
-        <v>41100003</v>
+        <v>41100319</v>
       </c>
       <c r="K17">
         <v>181148</v>
@@ -1041,391 +1014,434 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1">
         <v>411</v>
       </c>
       <c r="D18" s="2">
-        <v>41100265</v>
+        <v>41100325</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="C19" s="1">
-        <v>411</v>
-      </c>
-      <c r="D19" s="2">
-        <v>41100374</v>
-      </c>
+        <v>181145</v>
+      </c>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="1">
-        <v>411</v>
-      </c>
-      <c r="D20" s="2">
-        <v>41100662</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C20" s="3">
+        <v>181143</v>
+      </c>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1">
         <v>411</v>
       </c>
       <c r="D21" s="2">
-        <v>41100325</v>
+        <v>41100371</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1">
         <v>411</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
+      <c r="D22" s="2">
+        <v>41100282</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1">
         <v>411</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C24" s="1">
         <v>411</v>
       </c>
-      <c r="D24" s="2">
-        <v>41100112</v>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>38</v>
+      <c r="A25" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="C25" s="1">
         <v>411</v>
       </c>
       <c r="D25" s="2">
-        <v>41100379</v>
+        <v>41100011</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C26" s="1">
         <v>411</v>
       </c>
       <c r="D26" s="2">
-        <v>41100344</v>
+        <v>41100331</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1">
         <v>411</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>43</v>
+      <c r="D27" s="2">
+        <v>41100662</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1">
         <v>411</v>
       </c>
-      <c r="D28" s="2">
-        <v>41100331</v>
+      <c r="D28" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C29" s="1">
         <v>411</v>
       </c>
       <c r="D29" s="2">
-        <v>41100666</v>
+        <v>41100379</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C30" s="1">
         <v>411</v>
       </c>
       <c r="D30" s="2">
-        <v>41100645</v>
+        <v>41100311</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C31" s="1">
         <v>411</v>
       </c>
       <c r="D31" s="2">
-        <v>41100305</v>
+        <v>41100328</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1">
         <v>411</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>51</v>
+      <c r="D32" s="2">
+        <v>41100374</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
+      <c r="A33" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C33" s="1">
         <v>411</v>
       </c>
-      <c r="D33" s="2">
-        <v>41100010</v>
+      <c r="D33" s="1">
+        <v>41100009</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C34" s="1">
         <v>411</v>
       </c>
-      <c r="D34" s="2">
-        <v>41100185</v>
+      <c r="D34" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>55</v>
+      <c r="A35" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C35" s="1">
         <v>411</v>
       </c>
-      <c r="D35" s="2">
-        <v>41100311</v>
+      <c r="D35" s="1">
+        <v>41100661</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="3">
-        <v>181143</v>
-      </c>
-      <c r="D36" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="C36" s="1">
+        <v>411</v>
+      </c>
+      <c r="D36" s="2">
+        <v>41100645</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C37" s="1">
-        <v>181145</v>
-      </c>
-      <c r="D37" s="1"/>
+        <v>411</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="C38" s="1">
         <v>411</v>
       </c>
-      <c r="D38" s="4">
-        <v>41100358</v>
+      <c r="D38" s="2">
+        <v>41100096</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C39" s="1">
         <v>411</v>
       </c>
-      <c r="D39" s="4">
-        <v>41100313</v>
+      <c r="D39" s="2">
+        <v>41100666</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C40" s="1">
         <v>411</v>
       </c>
       <c r="D40" s="4">
-        <v>41100203</v>
+        <v>41100358</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C41" s="1">
         <v>411</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>70</v>
+      <c r="D41" s="2">
+        <v>41100344</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="C42" s="1">
         <v>411</v>
       </c>
       <c r="D42" s="8">
-        <v>41100290</v>
+        <v>41100125</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" s="1">
-        <v>411</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>79</v>
+        <v>4</v>
+      </c>
+      <c r="C43" s="9">
+        <v>411</v>
+      </c>
+      <c r="D43" s="8">
+        <v>41100118</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
+        <v>33</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C44" s="1">
         <v>411</v>
       </c>
-      <c r="D44" t="s">
-        <v>82</v>
+      <c r="D44" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C45" s="1"/>
+      <c r="A45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="1">
+        <v>411</v>
+      </c>
+      <c r="D45" s="2">
+        <v>41100112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="1">
+        <v>411</v>
+      </c>
+      <c r="D46">
+        <v>41100001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="1">
+        <v>411</v>
+      </c>
+      <c r="D47">
+        <v>41100007</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D44">
-    <sortState ref="A2:D44">
-      <sortCondition sortBy="cellColor" ref="A1:A44" dxfId="7"/>
+    <sortState ref="A2:D45">
+      <sortCondition ref="A1:A44"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D45 D48:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
